--- a/nr-add-profile-list/ig/StructureDefinition-fr-core-healthcare-service.xlsx
+++ b/nr-add-profile-list/ig/StructureDefinition-fr-core-healthcare-service.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2383" uniqueCount="431">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2384" uniqueCount="432">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-21T10:18:04+00:00</t>
+    <t>2024-03-21T10:58:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1257,7 +1257,10 @@
     <t>Indicates which days of the week are available between the start and end Times.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/days-of-week</t>
+    <t>The days of the week.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/days-of-week|4.0.1</t>
   </si>
   <si>
     <t>HealthcareService.availableTime.allDay</t>
@@ -5339,7 +5342,7 @@
         <v>75</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>216</v>
+        <v>171</v>
       </c>
       <c r="Y34" s="2"/>
       <c r="Z34" t="s" s="2">
@@ -7927,9 +7930,11 @@
       <c r="X58" t="s" s="2">
         <v>216</v>
       </c>
-      <c r="Y58" s="2"/>
+      <c r="Y58" t="s" s="2">
+        <v>399</v>
+      </c>
       <c r="Z58" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>75</v>
@@ -7970,10 +7975,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -7999,10 +8004,10 @@
         <v>261</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -8053,7 +8058,7 @@
         <v>75</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>76</v>
@@ -8076,10 +8081,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8102,16 +8107,16 @@
         <v>75</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -8161,7 +8166,7 @@
         <v>75</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>76</v>
@@ -8184,10 +8189,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8210,16 +8215,16 @@
         <v>75</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -8269,7 +8274,7 @@
         <v>75</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>76</v>
@@ -8292,10 +8297,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8321,10 +8326,10 @@
         <v>344</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -8375,7 +8380,7 @@
         <v>75</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>76</v>
@@ -8398,10 +8403,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -8504,10 +8509,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -8612,10 +8617,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -8722,10 +8727,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -8751,10 +8756,10 @@
         <v>100</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="N66" t="s" s="2">
         <v>305</v>
@@ -8807,7 +8812,7 @@
         <v>75</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>84</v>
@@ -8830,10 +8835,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -8859,10 +8864,10 @@
         <v>245</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="N67" t="s" s="2">
         <v>248</v>
@@ -8915,7 +8920,7 @@
         <v>75</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>76</v>
@@ -8938,10 +8943,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -8967,10 +8972,10 @@
         <v>100</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="N68" t="s" s="2">
         <v>305</v>
@@ -9023,7 +9028,7 @@
         <v>75</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>76</v>
@@ -9046,10 +9051,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9072,13 +9077,13 @@
         <v>75</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="N69" t="s" s="2">
         <v>299</v>
@@ -9131,7 +9136,7 @@
         <v>75</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>76</v>
@@ -9146,7 +9151,7 @@
         <v>258</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="AL69" t="s" s="2">
         <v>75</v>

--- a/nr-add-profile-list/ig/StructureDefinition-fr-core-healthcare-service.xlsx
+++ b/nr-add-profile-list/ig/StructureDefinition-fr-core-healthcare-service.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-21T10:58:03+00:00</t>
+    <t>2024-03-21T10:59:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-profile-list/ig/StructureDefinition-fr-core-healthcare-service.xlsx
+++ b/nr-add-profile-list/ig/StructureDefinition-fr-core-healthcare-service.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-21T10:59:21+00:00</t>
+    <t>2024-03-21T12:49:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-profile-list/ig/StructureDefinition-fr-core-healthcare-service.xlsx
+++ b/nr-add-profile-list/ig/StructureDefinition-fr-core-healthcare-service.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-21T12:49:37+00:00</t>
+    <t>2024-03-21T12:55:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-profile-list/ig/StructureDefinition-fr-core-healthcare-service.xlsx
+++ b/nr-add-profile-list/ig/StructureDefinition-fr-core-healthcare-service.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-21T12:55:50+00:00</t>
+    <t>2024-03-22T10:25:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-profile-list/ig/StructureDefinition-fr-core-healthcare-service.xlsx
+++ b/nr-add-profile-list/ig/StructureDefinition-fr-core-healthcare-service.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-22T10:25:22+00:00</t>
+    <t>2024-03-22T13:38:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-profile-list/ig/StructureDefinition-fr-core-healthcare-service.xlsx
+++ b/nr-add-profile-list/ig/StructureDefinition-fr-core-healthcare-service.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-22T13:38:23+00:00</t>
+    <t>2024-03-25T10:11:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
